--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-CapabilityStatement.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-CapabilityStatement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5908" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5919" uniqueCount="698">
   <si>
     <t>Property</t>
   </si>
@@ -499,6 +499,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>CapabilityStatement.meta.tag</t>
   </si>
   <si>
@@ -560,7 +567,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -938,10 +945,6 @@
     <t>May be a web site, an email address, a telephone number, etc.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Definition.contact</t>
   </si>
   <si>
@@ -1009,7 +1012,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
   </si>
   <si>
     <t>CD</t>
@@ -1086,7 +1089,7 @@
     <t>CapabilityStatement.instantiates</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CapabilityStatement|4.0.1)
+    <t xml:space="preserve">canonical(CapabilityStatement)
 </t>
   </si>
   <si>
@@ -1233,7 +1236,7 @@
     <t>CapabilityStatement.implementation.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1304,7 +1307,7 @@
     <t>CapabilityStatement.implementationGuide</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ImplementationGuide|4.0.1)
+    <t xml:space="preserve">canonical(ImplementationGuide)
 </t>
   </si>
   <si>
@@ -1415,7 +1418,7 @@
     <t>Types of security services used with FHIR.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/restful-security-service|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/restful-security-service</t>
   </si>
   <si>
     <t>CapabilityStatement.rest.security.description</t>
@@ -1470,6 +1473,10 @@
     <t>CapabilityStatement.rest.resource.profile</t>
   </si>
   <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
     <t>Base System profile for all uses of resource</t>
   </si>
   <si>
@@ -1741,7 +1748,7 @@
     <t>CapabilityStatement.rest.resource.searchParam.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(SearchParameter|4.0.1)
+    <t xml:space="preserve">canonical(SearchParameter)
 </t>
   </si>
   <si>
@@ -1846,7 +1853,7 @@
     <t>CapabilityStatement.rest.resource.operation.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(OperationDefinition|4.0.1)
+    <t xml:space="preserve">canonical(OperationDefinition)
 </t>
   </si>
   <si>
@@ -1961,7 +1968,7 @@
     <t>CapabilityStatement.rest.compartment</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CompartmentDefinition|4.0.1)
+    <t xml:space="preserve">canonical(CompartmentDefinition)
 </t>
   </si>
   <si>
@@ -2032,10 +2039,7 @@
     <t>The protocol used for message transport.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/message-transport|4.0.1</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>http://hl7.org/fhir/ValueSet/message-transport</t>
   </si>
   <si>
     <t>CapabilityStatement.messaging.endpoint.address</t>
@@ -2111,7 +2115,7 @@
     <t>CapabilityStatement.messaging.supportedMessage.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(MessageDefinition|4.0.1)
+    <t xml:space="preserve">canonical(MessageDefinition)
 </t>
   </si>
   <si>
@@ -3893,13 +3897,13 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
@@ -3913,10 +3917,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3942,13 +3946,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3974,13 +3978,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3998,7 +4002,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4007,13 +4011,13 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
@@ -4027,10 +4031,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4056,13 +4060,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4112,7 +4116,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4141,10 +4145,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4167,16 +4171,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4202,13 +4206,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4226,7 +4230,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4255,14 +4259,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4281,16 +4285,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4340,7 +4344,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4355,7 +4359,7 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
@@ -4369,14 +4373,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4395,16 +4399,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4454,7 +4458,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4469,7 +4473,7 @@
         <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
@@ -4483,10 +4487,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4515,7 +4519,7 @@
         <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
@@ -4568,7 +4572,7 @@
         <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4583,7 +4587,7 @@
         <v>116</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
@@ -4597,16 +4601,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4625,15 +4629,17 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4682,7 +4688,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4691,13 +4697,13 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
@@ -4711,16 +4717,16 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4739,15 +4745,17 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4796,7 +4804,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4805,13 +4813,13 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>78</v>
@@ -4825,16 +4833,16 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4853,15 +4861,17 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4910,7 +4920,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4919,13 +4929,13 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
@@ -4939,13 +4949,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4967,16 +4977,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5026,7 +5036,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5055,13 +5065,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -5083,16 +5093,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5142,7 +5152,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5171,13 +5181,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -5199,16 +5209,16 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5258,7 +5268,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5287,10 +5297,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5316,16 +5326,16 @@
         <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5374,7 +5384,7 @@
         <v>114</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5389,7 +5399,7 @@
         <v>116</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
@@ -5403,10 +5413,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5432,16 +5442,16 @@
         <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5490,7 +5500,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5508,10 +5518,10 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5519,10 +5529,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5548,13 +5558,13 @@
         <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5604,7 +5614,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5622,10 +5632,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5633,10 +5643,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5662,16 +5672,16 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5720,7 +5730,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5729,7 +5739,7 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
@@ -5749,10 +5759,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5778,13 +5788,13 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5834,7 +5844,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5852,7 +5862,7 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5863,10 +5873,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5889,16 +5899,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5924,13 +5934,13 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5948,7 +5958,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5966,10 +5976,10 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5977,10 +5987,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6003,19 +6013,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6064,7 +6074,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6082,10 +6092,10 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -6093,14 +6103,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6119,16 +6129,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6178,7 +6188,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -6196,10 +6206,10 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -6207,10 +6217,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6236,16 +6246,16 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6294,7 +6304,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6312,10 +6322,10 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -6323,10 +6333,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6349,16 +6359,16 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6408,7 +6418,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6417,7 +6427,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
@@ -6426,7 +6436,7 @@
         <v>86</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6437,10 +6447,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6463,16 +6473,16 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6522,7 +6532,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6531,7 +6541,7 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
@@ -6540,7 +6550,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6551,10 +6561,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6577,19 +6587,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6638,7 +6648,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6647,7 +6657,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
@@ -6656,7 +6666,7 @@
         <v>86</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6667,10 +6677,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6693,16 +6703,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6731,10 +6741,10 @@
         <v>151</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -6752,7 +6762,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6761,16 +6771,16 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6781,10 +6791,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6807,16 +6817,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6866,7 +6876,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6884,25 +6894,25 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6921,19 +6931,19 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6982,7 +6992,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7000,21 +7010,21 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7037,17 +7047,17 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7072,13 +7082,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -7096,7 +7106,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>88</v>
@@ -7105,7 +7115,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -7125,10 +7135,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7151,16 +7161,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7210,7 +7220,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7239,10 +7249,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7265,16 +7275,16 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7324,7 +7334,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7353,10 +7363,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7379,13 +7389,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7436,7 +7446,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7445,7 +7455,7 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
@@ -7465,10 +7475,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7577,10 +7587,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7691,14 +7701,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7720,16 +7730,16 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7778,7 +7788,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7793,7 +7803,7 @@
         <v>116</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>78</v>
@@ -7807,10 +7817,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7836,13 +7846,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7892,7 +7902,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>88</v>
@@ -7921,10 +7931,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7950,13 +7960,13 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8006,7 +8016,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8035,10 +8045,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8061,13 +8071,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8118,7 +8128,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8147,10 +8157,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8173,13 +8183,13 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8230,7 +8240,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8239,7 +8249,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -8259,10 +8269,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8371,10 +8381,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8485,14 +8495,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8514,16 +8524,16 @@
         <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8572,7 +8582,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8587,7 +8597,7 @@
         <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
@@ -8601,10 +8611,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8630,13 +8640,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8686,7 +8696,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>88</v>
@@ -8715,10 +8725,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8741,13 +8751,13 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8798,7 +8808,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8827,10 +8837,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8853,16 +8863,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8912,7 +8922,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8921,13 +8931,13 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8941,10 +8951,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8967,16 +8977,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9002,13 +9012,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -9026,7 +9036,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>88</v>
@@ -9055,10 +9065,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9081,16 +9091,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9116,13 +9126,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9140,7 +9150,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>88</v>
@@ -9169,10 +9179,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9195,16 +9205,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9230,13 +9240,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9254,7 +9264,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9283,10 +9293,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9309,16 +9319,16 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9368,7 +9378,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9397,10 +9407,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9423,16 +9433,16 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9482,7 +9492,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9491,10 +9501,10 @@
         <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>86</v>
@@ -9511,10 +9521,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9623,10 +9633,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9737,14 +9747,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9766,16 +9776,16 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9824,7 +9834,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9839,7 +9849,7 @@
         <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
@@ -9853,10 +9863,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9879,13 +9889,13 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9912,13 +9922,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9936,7 +9946,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>88</v>
@@ -9965,10 +9975,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9991,16 +10001,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10050,7 +10060,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10079,10 +10089,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10105,13 +10115,13 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10162,7 +10172,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10171,7 +10181,7 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>100</v>
@@ -10191,10 +10201,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10303,10 +10313,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10417,14 +10427,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10446,16 +10456,16 @@
         <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10504,7 +10514,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10519,7 +10529,7 @@
         <v>116</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>78</v>
@@ -10533,10 +10543,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10559,16 +10569,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10618,7 +10628,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10647,10 +10657,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10673,16 +10683,16 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10711,10 +10721,10 @@
         <v>151</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10732,7 +10742,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10741,13 +10751,13 @@
         <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>78</v>
@@ -10761,10 +10771,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10787,16 +10797,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10846,7 +10856,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10875,10 +10885,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10901,16 +10911,16 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10960,7 +10970,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10969,10 +10979,10 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>86</v>
@@ -10989,10 +10999,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11101,10 +11111,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11215,14 +11225,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11244,16 +11254,16 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11302,7 +11312,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11317,7 +11327,7 @@
         <v>116</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>78</v>
@@ -11331,10 +11341,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11357,13 +11367,13 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11390,13 +11400,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11414,7 +11424,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11443,10 +11453,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11469,16 +11479,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>135</v>
+        <v>466</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11528,7 +11538,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11557,10 +11567,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11583,16 +11593,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>135</v>
+        <v>466</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11642,7 +11652,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11671,10 +11681,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11697,16 +11707,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11756,7 +11766,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11785,10 +11795,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11811,16 +11821,16 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11870,7 +11880,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11879,7 +11889,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>100</v>
@@ -11899,10 +11909,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12011,10 +12021,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12125,16 +12135,16 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12153,15 +12163,17 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -12219,13 +12231,13 @@
         <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>78</v>
@@ -12239,16 +12251,16 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="B86" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="C86" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12267,15 +12279,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12333,13 +12347,13 @@
         <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>78</v>
@@ -12353,16 +12367,16 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12381,16 +12395,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12449,13 +12463,13 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>78</v>
@@ -12469,14 +12483,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12498,16 +12512,16 @@
         <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12556,7 +12570,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12571,7 +12585,7 @@
         <v>116</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>78</v>
@@ -12585,10 +12599,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12611,13 +12625,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12644,13 +12658,13 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -12668,7 +12682,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>88</v>
@@ -12697,10 +12711,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12723,19 +12737,19 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12784,7 +12798,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12813,10 +12827,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12839,16 +12853,16 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12874,13 +12888,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12898,7 +12912,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12927,10 +12941,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12953,16 +12967,16 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13012,7 +13026,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13041,10 +13055,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13067,16 +13081,16 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13126,7 +13140,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13155,10 +13169,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13181,16 +13195,16 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13240,7 +13254,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13269,10 +13283,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13295,16 +13309,16 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13330,31 +13344,31 @@
         <v>78</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13383,10 +13397,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13409,16 +13423,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13468,7 +13482,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13497,10 +13511,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13523,16 +13537,16 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13558,31 +13572,31 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13611,10 +13625,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13637,13 +13651,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13670,31 +13684,31 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13723,10 +13737,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13752,13 +13766,13 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13808,7 +13822,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13837,10 +13851,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13866,13 +13880,13 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13922,7 +13936,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13951,10 +13965,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13977,16 +13991,16 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14036,7 +14050,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14045,7 +14059,7 @@
         <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>100</v>
@@ -14065,10 +14079,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14177,10 +14191,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14291,14 +14305,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14320,16 +14334,16 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14378,7 +14392,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14393,7 +14407,7 @@
         <v>116</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>78</v>
@@ -14407,10 +14421,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14436,13 +14450,13 @@
         <v>102</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14492,7 +14506,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>88</v>
@@ -14521,10 +14535,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14547,16 +14561,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14606,7 +14620,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14635,10 +14649,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14661,16 +14675,16 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14696,13 +14710,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14720,7 +14734,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>88</v>
@@ -14749,10 +14763,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14775,16 +14789,16 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14834,7 +14848,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14863,10 +14877,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14889,16 +14903,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14948,7 +14962,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14957,7 +14971,7 @@
         <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>100</v>
@@ -14977,10 +14991,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15089,10 +15103,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15203,16 +15217,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15231,15 +15245,17 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15297,13 +15313,13 @@
         <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>78</v>
@@ -15317,16 +15333,16 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="B113" t="s" s="2">
-        <v>573</v>
-      </c>
       <c r="C113" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15345,15 +15361,17 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15411,13 +15429,13 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>78</v>
@@ -15431,23 +15449,23 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
@@ -15459,15 +15477,17 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15525,13 +15545,13 @@
         <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>78</v>
@@ -15545,16 +15565,16 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15573,16 +15593,16 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15641,13 +15661,13 @@
         <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>78</v>
@@ -15661,14 +15681,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15690,16 +15710,16 @@
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -15748,7 +15768,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15763,7 +15783,7 @@
         <v>116</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>78</v>
@@ -15777,10 +15797,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15806,13 +15826,13 @@
         <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15862,7 +15882,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>88</v>
@@ -15891,10 +15911,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15917,16 +15937,16 @@
         <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15976,7 +15996,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>88</v>
@@ -16005,10 +16025,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16031,16 +16051,16 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16090,7 +16110,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16119,10 +16139,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16145,13 +16165,13 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16202,7 +16222,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16211,7 +16231,7 @@
         <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -16231,10 +16251,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16343,10 +16363,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16457,14 +16477,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16486,16 +16506,16 @@
         <v>108</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16544,7 +16564,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16559,7 +16579,7 @@
         <v>116</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>78</v>
@@ -16573,10 +16593,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16599,13 +16619,13 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16632,13 +16652,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -16656,7 +16676,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>88</v>
@@ -16685,10 +16705,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16711,16 +16731,16 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16770,7 +16790,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16799,10 +16819,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16828,13 +16848,13 @@
         <v>81</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16884,7 +16904,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16913,10 +16933,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16939,16 +16959,16 @@
         <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16998,7 +17018,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17027,10 +17047,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17139,10 +17159,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17253,16 +17273,16 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17281,15 +17301,17 @@
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17347,13 +17369,13 @@
         <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>78</v>
@@ -17367,16 +17389,16 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="B131" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="C131" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17395,15 +17417,17 @@
         <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -17461,13 +17485,13 @@
         <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>78</v>
@@ -17481,23 +17505,23 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>78</v>
@@ -17509,15 +17533,17 @@
         <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17575,13 +17601,13 @@
         <v>80</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>78</v>
@@ -17595,16 +17621,16 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -17623,16 +17649,16 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17691,13 +17717,13 @@
         <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>78</v>
@@ -17711,14 +17737,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -17740,16 +17766,16 @@
         <v>108</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17798,7 +17824,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17813,7 +17839,7 @@
         <v>116</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>78</v>
@@ -17827,10 +17853,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17856,13 +17882,13 @@
         <v>102</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17912,7 +17938,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>88</v>
@@ -17941,10 +17967,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17967,16 +17993,16 @@
         <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18026,7 +18052,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>88</v>
@@ -18055,10 +18081,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18081,16 +18107,16 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18140,7 +18166,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18169,10 +18195,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18195,16 +18221,16 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18254,7 +18280,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18283,10 +18309,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18309,16 +18335,16 @@
         <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18368,7 +18394,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18377,7 +18403,7 @@
         <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>100</v>
@@ -18397,10 +18423,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18509,10 +18535,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18623,14 +18649,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -18652,16 +18678,16 @@
         <v>108</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18710,7 +18736,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18725,7 +18751,7 @@
         <v>116</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>78</v>
@@ -18739,14 +18765,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -18765,13 +18791,13 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18822,7 +18848,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18831,7 +18857,7 @@
         <v>80</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>100</v>
@@ -18851,10 +18877,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18963,10 +18989,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19077,14 +19103,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19106,16 +19132,16 @@
         <v>108</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19164,7 +19190,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19179,7 +19205,7 @@
         <v>116</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>78</v>
@@ -19193,10 +19219,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19222,13 +19248,13 @@
         <v>147</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19257,10 +19283,10 @@
         <v>151</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>78</v>
@@ -19278,7 +19304,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>88</v>
@@ -19287,13 +19313,13 @@
         <v>88</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>651</v>
+        <v>156</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>78</v>
@@ -19307,10 +19333,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19333,13 +19359,13 @@
         <v>78</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19390,7 +19416,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>88</v>
@@ -19419,10 +19445,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19445,16 +19471,16 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19504,7 +19530,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19533,10 +19559,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19559,16 +19585,16 @@
         <v>78</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19618,7 +19644,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -19647,10 +19673,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19673,16 +19699,16 @@
         <v>89</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19732,7 +19758,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -19741,7 +19767,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>100</v>
@@ -19761,10 +19787,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19873,10 +19899,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19987,14 +20013,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20016,16 +20042,16 @@
         <v>108</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -20074,7 +20100,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20089,7 +20115,7 @@
         <v>116</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>78</v>
@@ -20103,10 +20129,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20129,13 +20155,13 @@
         <v>89</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20162,13 +20188,13 @@
         <v>78</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>78</v>
@@ -20186,7 +20212,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>88</v>
@@ -20215,10 +20241,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20241,16 +20267,16 @@
         <v>89</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20300,7 +20326,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>88</v>
@@ -20329,10 +20355,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20355,13 +20381,13 @@
         <v>89</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20412,7 +20438,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -20421,7 +20447,7 @@
         <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>100</v>
@@ -20441,10 +20467,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20553,10 +20579,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20667,14 +20693,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -20696,16 +20722,16 @@
         <v>108</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -20754,7 +20780,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -20769,7 +20795,7 @@
         <v>116</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>78</v>
@@ -20783,10 +20809,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20809,13 +20835,13 @@
         <v>89</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20842,13 +20868,13 @@
         <v>78</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>78</v>
@@ -20866,7 +20892,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>88</v>
@@ -20895,10 +20921,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20921,16 +20947,16 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -20980,7 +21006,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21009,10 +21035,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21035,16 +21061,16 @@
         <v>89</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>135</v>
+        <v>466</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21094,7 +21120,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>88</v>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-CapabilityStatement.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-CapabilityStatement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5919" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5908" uniqueCount="697">
   <si>
     <t>Property</t>
   </si>
@@ -499,13 +499,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>CapabilityStatement.meta.tag</t>
   </si>
   <si>
@@ -567,7 +560,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -945,6 +938,10 @@
     <t>May be a web site, an email address, a telephone number, etc.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Definition.contact</t>
   </si>
   <si>
@@ -1012,7 +1009,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>CD</t>
@@ -1089,7 +1086,7 @@
     <t>CapabilityStatement.instantiates</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CapabilityStatement)
+    <t xml:space="preserve">canonical(CapabilityStatement|4.0.1)
 </t>
   </si>
   <si>
@@ -1236,7 +1233,7 @@
     <t>CapabilityStatement.implementation.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1307,7 +1304,7 @@
     <t>CapabilityStatement.implementationGuide</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ImplementationGuide)
+    <t xml:space="preserve">canonical(ImplementationGuide|4.0.1)
 </t>
   </si>
   <si>
@@ -1418,7 +1415,7 @@
     <t>Types of security services used with FHIR.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/restful-security-service</t>
+    <t>http://hl7.org/fhir/ValueSet/restful-security-service|4.0.1</t>
   </si>
   <si>
     <t>CapabilityStatement.rest.security.description</t>
@@ -1473,10 +1470,6 @@
     <t>CapabilityStatement.rest.resource.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
     <t>Base System profile for all uses of resource</t>
   </si>
   <si>
@@ -1748,7 +1741,7 @@
     <t>CapabilityStatement.rest.resource.searchParam.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(SearchParameter)
+    <t xml:space="preserve">canonical(SearchParameter|4.0.1)
 </t>
   </si>
   <si>
@@ -1853,7 +1846,7 @@
     <t>CapabilityStatement.rest.resource.operation.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(OperationDefinition)
+    <t xml:space="preserve">canonical(OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1968,7 +1961,7 @@
     <t>CapabilityStatement.rest.compartment</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CompartmentDefinition)
+    <t xml:space="preserve">canonical(CompartmentDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -2039,7 +2032,10 @@
     <t>The protocol used for message transport.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/message-transport</t>
+    <t>http://hl7.org/fhir/ValueSet/message-transport|4.0.1</t>
+  </si>
+  <si>
+    <t>CV</t>
   </si>
   <si>
     <t>CapabilityStatement.messaging.endpoint.address</t>
@@ -2115,7 +2111,7 @@
     <t>CapabilityStatement.messaging.supportedMessage.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(MessageDefinition)
+    <t xml:space="preserve">canonical(MessageDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -3897,13 +3893,13 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
@@ -3917,10 +3913,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3946,13 +3942,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3978,31 +3974,31 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4011,13 +4007,13 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
@@ -4031,10 +4027,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4060,13 +4056,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4116,7 +4112,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4145,10 +4141,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4171,16 +4167,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4206,31 +4202,31 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4259,14 +4255,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4285,16 +4281,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4344,7 +4340,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4359,7 +4355,7 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
@@ -4373,14 +4369,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4399,16 +4395,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4458,7 +4454,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4473,7 +4469,7 @@
         <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
@@ -4487,10 +4483,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4519,7 +4515,7 @@
         <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
@@ -4572,7 +4568,7 @@
         <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4587,7 +4583,7 @@
         <v>116</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
@@ -4601,16 +4597,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4629,17 +4625,15 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4688,7 +4682,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4697,13 +4691,13 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
@@ -4717,16 +4711,16 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4745,17 +4739,15 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4804,7 +4796,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4813,13 +4805,13 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>78</v>
@@ -4833,16 +4825,16 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4861,17 +4853,15 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4920,7 +4910,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4929,13 +4919,13 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
@@ -4949,13 +4939,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4977,16 +4967,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5036,7 +5026,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5065,13 +5055,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -5093,16 +5083,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5152,7 +5142,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5181,13 +5171,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -5209,16 +5199,16 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5268,7 +5258,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5297,10 +5287,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5326,16 +5316,16 @@
         <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5384,7 +5374,7 @@
         <v>114</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5399,7 +5389,7 @@
         <v>116</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
@@ -5413,10 +5403,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5442,16 +5432,16 @@
         <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5500,7 +5490,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5518,10 +5508,10 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5529,10 +5519,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5558,13 +5548,13 @@
         <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5614,7 +5604,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5632,10 +5622,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5643,10 +5633,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5672,16 +5662,16 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5730,7 +5720,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5739,7 +5729,7 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
@@ -5759,10 +5749,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5788,13 +5778,13 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5844,7 +5834,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5862,7 +5852,7 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5873,10 +5863,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5899,16 +5889,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5934,14 +5924,14 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5958,7 +5948,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5976,10 +5966,10 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5987,10 +5977,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6013,19 +6003,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6074,7 +6064,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6092,10 +6082,10 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -6103,14 +6093,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6129,16 +6119,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6188,7 +6178,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -6206,10 +6196,10 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -6217,10 +6207,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6246,16 +6236,16 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6304,7 +6294,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6322,10 +6312,10 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -6333,10 +6323,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6359,16 +6349,16 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6418,7 +6408,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6427,7 +6417,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
@@ -6436,7 +6426,7 @@
         <v>86</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6447,10 +6437,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6473,16 +6463,16 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6532,7 +6522,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6541,7 +6531,7 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
@@ -6550,7 +6540,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6561,10 +6551,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6587,19 +6577,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6648,7 +6638,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6657,7 +6647,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
@@ -6666,7 +6656,7 @@
         <v>86</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6677,10 +6667,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6703,16 +6693,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6741,11 +6731,11 @@
         <v>151</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6762,7 +6752,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6771,16 +6761,16 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6791,10 +6781,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6817,16 +6807,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6876,7 +6866,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6894,25 +6884,25 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6931,19 +6921,19 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6992,7 +6982,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7010,21 +7000,21 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7047,17 +7037,17 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7082,40 +7072,40 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI40" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -7135,10 +7125,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7161,16 +7151,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7220,7 +7210,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7249,10 +7239,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7275,16 +7265,16 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7334,7 +7324,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7363,10 +7353,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7389,13 +7379,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7446,7 +7436,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7455,7 +7445,7 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
@@ -7475,10 +7465,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7587,10 +7577,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7701,14 +7691,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7730,16 +7720,16 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7788,7 +7778,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7803,7 +7793,7 @@
         <v>116</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>78</v>
@@ -7817,10 +7807,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7846,13 +7836,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7902,7 +7892,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>88</v>
@@ -7931,10 +7921,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7960,13 +7950,13 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8016,7 +8006,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8045,10 +8035,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8071,13 +8061,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8128,7 +8118,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8157,10 +8147,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8183,13 +8173,13 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8240,7 +8230,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8249,7 +8239,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -8269,10 +8259,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8381,10 +8371,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8495,14 +8485,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8524,16 +8514,16 @@
         <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8582,7 +8572,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8597,7 +8587,7 @@
         <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
@@ -8611,10 +8601,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8640,13 +8630,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8696,7 +8686,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>88</v>
@@ -8725,10 +8715,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8751,13 +8741,13 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8808,7 +8798,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8837,10 +8827,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8863,16 +8853,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8922,7 +8912,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8931,13 +8921,13 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AK56" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8951,10 +8941,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8977,16 +8967,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9012,14 +9002,14 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
       </c>
@@ -9036,7 +9026,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>88</v>
@@ -9065,10 +9055,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9091,16 +9081,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9126,14 +9116,14 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9150,7 +9140,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>88</v>
@@ -9179,10 +9169,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9205,16 +9195,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9240,31 +9230,31 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z59" t="s" s="2">
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9293,10 +9283,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9319,16 +9309,16 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9378,7 +9368,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9407,10 +9397,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9433,16 +9423,16 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9492,7 +9482,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9501,10 +9491,10 @@
         <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>86</v>
@@ -9521,10 +9511,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9633,10 +9623,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9747,14 +9737,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9776,16 +9766,16 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9834,7 +9824,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9849,7 +9839,7 @@
         <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
@@ -9863,10 +9853,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9889,13 +9879,13 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9922,14 +9912,14 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>429</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9946,7 +9936,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>88</v>
@@ -9975,10 +9965,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10001,16 +9991,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="N66" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10060,7 +10050,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10089,10 +10079,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10115,13 +10105,13 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10172,7 +10162,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10181,7 +10171,7 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>100</v>
@@ -10201,10 +10191,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10313,10 +10303,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10427,14 +10417,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10456,16 +10446,16 @@
         <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10514,7 +10504,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10529,7 +10519,7 @@
         <v>116</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>78</v>
@@ -10543,10 +10533,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10569,16 +10559,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10628,7 +10618,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10657,10 +10647,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10683,16 +10673,16 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10721,11 +10711,11 @@
         <v>151</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10742,7 +10732,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10751,13 +10741,13 @@
         <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>78</v>
@@ -10771,10 +10761,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10797,16 +10787,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M73" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="N73" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10856,7 +10846,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10885,10 +10875,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10911,16 +10901,16 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10970,7 +10960,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10979,10 +10969,10 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>86</v>
@@ -10999,10 +10989,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11111,10 +11101,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11225,14 +11215,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11254,16 +11244,16 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11312,7 +11302,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11327,7 +11317,7 @@
         <v>116</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>78</v>
@@ -11341,10 +11331,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11367,13 +11357,13 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11400,14 +11390,14 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11424,7 +11414,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11453,10 +11443,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11479,16 +11469,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11538,7 +11528,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11567,10 +11557,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11593,16 +11583,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>466</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11652,7 +11642,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11681,10 +11671,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11707,16 +11697,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11766,7 +11756,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11795,10 +11785,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11821,16 +11811,16 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11880,7 +11870,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11889,7 +11879,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>100</v>
@@ -11909,10 +11899,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12021,10 +12011,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12135,16 +12125,16 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12163,17 +12153,15 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -12231,13 +12219,13 @@
         <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>78</v>
@@ -12251,16 +12239,16 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12279,17 +12267,15 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L86" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12347,13 +12333,13 @@
         <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>78</v>
@@ -12367,16 +12353,16 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12395,16 +12381,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12463,13 +12449,13 @@
         <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>78</v>
@@ -12483,14 +12469,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12512,16 +12498,16 @@
         <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12570,7 +12556,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12585,7 +12571,7 @@
         <v>116</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>78</v>
@@ -12599,10 +12585,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12625,13 +12611,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12658,13 +12644,13 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -12682,7 +12668,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>88</v>
@@ -12711,10 +12697,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12737,19 +12723,19 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O90" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12798,7 +12784,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12827,10 +12813,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12853,16 +12839,16 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12888,13 +12874,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12912,7 +12898,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12941,10 +12927,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12967,16 +12953,16 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13026,7 +13012,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13055,10 +13041,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13081,16 +13067,16 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13140,7 +13126,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13169,10 +13155,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13195,16 +13181,16 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13254,7 +13240,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13283,10 +13269,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13309,16 +13295,16 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13344,14 +13330,14 @@
         <v>78</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13368,7 +13354,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13397,10 +13383,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13423,16 +13409,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13482,7 +13468,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13511,10 +13497,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13537,16 +13523,16 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13572,14 +13558,14 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13596,7 +13582,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13625,10 +13611,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13651,13 +13637,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13684,13 +13670,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -13708,7 +13694,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13737,10 +13723,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13766,13 +13752,13 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13822,7 +13808,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13851,10 +13837,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13880,13 +13866,13 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13936,7 +13922,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13965,10 +13951,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13991,16 +13977,16 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14050,7 +14036,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14059,7 +14045,7 @@
         <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>100</v>
@@ -14079,10 +14065,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14191,10 +14177,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14305,14 +14291,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14334,16 +14320,16 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14392,7 +14378,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14407,7 +14393,7 @@
         <v>116</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>78</v>
@@ -14421,10 +14407,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14450,13 +14436,13 @@
         <v>102</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14506,7 +14492,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>88</v>
@@ -14535,10 +14521,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14561,16 +14547,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14620,7 +14606,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14649,10 +14635,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14675,16 +14661,16 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14710,13 +14696,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14734,7 +14720,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>88</v>
@@ -14763,10 +14749,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14789,16 +14775,16 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14848,7 +14834,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14877,10 +14863,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14903,16 +14889,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14962,7 +14948,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14971,7 +14957,7 @@
         <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>100</v>
@@ -14991,10 +14977,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15103,10 +15089,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15217,16 +15203,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15245,17 +15231,15 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L112" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15313,13 +15297,13 @@
         <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>78</v>
@@ -15333,16 +15317,16 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15361,17 +15345,15 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L113" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15429,13 +15411,13 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>78</v>
@@ -15449,45 +15431,43 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="H114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L114" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15545,13 +15525,13 @@
         <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>78</v>
@@ -15565,16 +15545,16 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15593,16 +15573,16 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15661,13 +15641,13 @@
         <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>78</v>
@@ -15681,14 +15661,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15710,16 +15690,16 @@
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -15768,7 +15748,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15783,7 +15763,7 @@
         <v>116</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>78</v>
@@ -15797,10 +15777,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15826,13 +15806,13 @@
         <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15882,7 +15862,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>88</v>
@@ -15911,10 +15891,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15937,16 +15917,16 @@
         <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15996,7 +15976,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>88</v>
@@ -16025,10 +16005,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16051,16 +16031,16 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16110,7 +16090,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16139,10 +16119,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16165,13 +16145,13 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16222,7 +16202,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16231,7 +16211,7 @@
         <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -16251,10 +16231,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16363,10 +16343,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16477,14 +16457,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16506,16 +16486,16 @@
         <v>108</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16564,7 +16544,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16579,7 +16559,7 @@
         <v>116</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>78</v>
@@ -16593,10 +16573,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16619,13 +16599,13 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16652,13 +16632,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -16676,7 +16656,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>88</v>
@@ -16705,10 +16685,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16731,16 +16711,16 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16790,7 +16770,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16819,10 +16799,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16848,13 +16828,13 @@
         <v>81</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N126" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16904,7 +16884,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16933,10 +16913,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16959,16 +16939,16 @@
         <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17018,7 +16998,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17047,10 +17027,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17159,10 +17139,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17273,16 +17253,16 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17301,17 +17281,15 @@
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L130" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17369,13 +17347,13 @@
         <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>78</v>
@@ -17389,16 +17367,16 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17417,17 +17395,15 @@
         <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L131" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -17485,13 +17461,13 @@
         <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>78</v>
@@ -17505,45 +17481,43 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="H132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L132" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17601,13 +17575,13 @@
         <v>80</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>78</v>
@@ -17621,16 +17595,16 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -17649,16 +17623,16 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17717,13 +17691,13 @@
         <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>78</v>
@@ -17737,14 +17711,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -17766,16 +17740,16 @@
         <v>108</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17824,7 +17798,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17839,7 +17813,7 @@
         <v>116</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>78</v>
@@ -17853,10 +17827,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17882,13 +17856,13 @@
         <v>102</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17938,7 +17912,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>88</v>
@@ -17967,10 +17941,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17993,16 +17967,16 @@
         <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18052,7 +18026,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>88</v>
@@ -18081,10 +18055,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18107,16 +18081,16 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18166,7 +18140,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18195,10 +18169,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18221,16 +18195,16 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18280,7 +18254,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18309,10 +18283,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18335,16 +18309,16 @@
         <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18394,7 +18368,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18403,7 +18377,7 @@
         <v>80</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>100</v>
@@ -18423,10 +18397,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18535,10 +18509,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18649,14 +18623,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -18678,16 +18652,16 @@
         <v>108</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -18736,7 +18710,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18751,7 +18725,7 @@
         <v>116</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>78</v>
@@ -18765,14 +18739,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -18791,13 +18765,13 @@
         <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -18848,7 +18822,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -18857,7 +18831,7 @@
         <v>80</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>100</v>
@@ -18877,10 +18851,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18989,10 +18963,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19103,14 +19077,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19132,16 +19106,16 @@
         <v>108</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19190,7 +19164,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19205,7 +19179,7 @@
         <v>116</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>78</v>
@@ -19219,10 +19193,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19248,13 +19222,13 @@
         <v>147</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19283,10 +19257,10 @@
         <v>151</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>78</v>
@@ -19304,7 +19278,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>88</v>
@@ -19313,13 +19287,13 @@
         <v>88</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>156</v>
+        <v>651</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>78</v>
@@ -19333,10 +19307,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19359,13 +19333,13 @@
         <v>78</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19416,7 +19390,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>88</v>
@@ -19445,10 +19419,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19471,16 +19445,16 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19530,7 +19504,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19559,10 +19533,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19585,16 +19559,16 @@
         <v>78</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M150" t="s" s="2">
-        <v>663</v>
-      </c>
       <c r="N150" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19644,7 +19618,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -19673,10 +19647,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19699,16 +19673,16 @@
         <v>89</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -19758,7 +19732,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -19767,7 +19741,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>100</v>
@@ -19787,10 +19761,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19899,10 +19873,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20013,14 +19987,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20042,16 +20016,16 @@
         <v>108</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -20100,7 +20074,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20115,7 +20089,7 @@
         <v>116</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>78</v>
@@ -20129,10 +20103,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20155,13 +20129,13 @@
         <v>89</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20188,14 +20162,14 @@
         <v>78</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y155" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="Z155" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="Z155" t="s" s="2">
-        <v>675</v>
-      </c>
       <c r="AA155" t="s" s="2">
         <v>78</v>
       </c>
@@ -20212,7 +20186,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>88</v>
@@ -20241,10 +20215,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20267,16 +20241,16 @@
         <v>89</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="M156" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="N156" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20326,7 +20300,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>88</v>
@@ -20355,10 +20329,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20381,13 +20355,13 @@
         <v>89</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20438,7 +20412,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -20447,7 +20421,7 @@
         <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>100</v>
@@ -20467,10 +20441,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20579,10 +20553,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20693,14 +20667,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -20722,16 +20696,16 @@
         <v>108</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -20780,7 +20754,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -20795,7 +20769,7 @@
         <v>116</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>78</v>
@@ -20809,10 +20783,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20835,13 +20809,13 @@
         <v>89</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20868,14 +20842,14 @@
         <v>78</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y161" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="Z161" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="Z161" t="s" s="2">
-        <v>690</v>
-      </c>
       <c r="AA161" t="s" s="2">
         <v>78</v>
       </c>
@@ -20892,7 +20866,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>88</v>
@@ -20921,10 +20895,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20947,16 +20921,16 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="M162" t="s" s="2">
-        <v>693</v>
-      </c>
       <c r="N162" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21006,7 +20980,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21035,10 +21009,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21061,16 +21035,16 @@
         <v>89</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>466</v>
+        <v>135</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21120,7 +21094,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>88</v>
